--- a/automation-repository/fixtures/config-uploads/reg-cancel-031.xlsx
+++ b/automation-repository/fixtures/config-uploads/reg-cancel-031.xlsx
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GHNG-1000008364-J</v>
+        <v>GHNG-1000008364-Q</v>
       </c>
       <c r="B2">
         <v>1</v>
